--- a/Data/TestData/CM_Matser.xlsx
+++ b/Data/TestData/CM_Matser.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E5D6D5-A001-46AF-8B4D-0666A712B0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDE93B8-8638-4252-9A76-EBE2ABFDCAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,13 +42,13 @@
     <t>cm_Name</t>
   </si>
   <si>
-    <t>c10092039</t>
-  </si>
-  <si>
-    <t>CMa10939</t>
-  </si>
-  <si>
     <t>BMOPT4884E</t>
+  </si>
+  <si>
+    <t>c10092041</t>
+  </si>
+  <si>
+    <t>CMa10941</t>
   </si>
 </sst>
 </file>
@@ -397,13 +397,13 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Data/TestData/CM_Matser.xlsx
+++ b/Data/TestData/CM_Matser.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDE93B8-8638-4252-9A76-EBE2ABFDCAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1884850-918F-4473-A9B7-544CB6E167EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1200" yWindow="255" windowWidth="8520" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -45,10 +45,10 @@
     <t>BMOPT4884E</t>
   </si>
   <si>
-    <t>c10092041</t>
-  </si>
-  <si>
-    <t>CMa10941</t>
+    <t>c10092042</t>
+  </si>
+  <si>
+    <t>CMa10942</t>
   </si>
 </sst>
 </file>

--- a/Data/TestData/CM_Matser.xlsx
+++ b/Data/TestData/CM_Matser.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1884850-918F-4473-A9B7-544CB6E167EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E15F96-A8BB-4A07-8842-217F460E4029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="255" windowWidth="8520" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Data/TestData/CM_Matser.xlsx
+++ b/Data/TestData/CM_Matser.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E15F96-A8BB-4A07-8842-217F460E4029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE252847-8056-447E-B042-70EB481491DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Data/TestData/CM_Matser.xlsx
+++ b/Data/TestData/CM_Matser.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE252847-8056-447E-B042-70EB481491DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C9167C-EA86-4E2B-8864-08A5254A86FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,13 +42,13 @@
     <t>cm_Name</t>
   </si>
   <si>
-    <t>BMOPT4884E</t>
-  </si>
-  <si>
-    <t>c10092042</t>
-  </si>
-  <si>
-    <t>CMa10942</t>
+    <t>c10092043</t>
+  </si>
+  <si>
+    <t>CMa10943</t>
+  </si>
+  <si>
+    <t>BMOPT4884H</t>
   </si>
 </sst>
 </file>
@@ -397,13 +397,13 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Data/TestData/CM_Matser.xlsx
+++ b/Data/TestData/CM_Matser.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C9167C-EA86-4E2B-8864-08A5254A86FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D1219E-2EB0-47E4-A0B3-D7578F1969DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Data/TestData/CM_Matser.xlsx
+++ b/Data/TestData/CM_Matser.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D1219E-2EB0-47E4-A0B3-D7578F1969DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F9DCD86-E026-4CF3-AF58-E097592F7D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,13 +42,13 @@
     <t>cm_Name</t>
   </si>
   <si>
-    <t>c10092043</t>
-  </si>
-  <si>
-    <t>CMa10943</t>
-  </si>
-  <si>
     <t>BMOPT4884H</t>
+  </si>
+  <si>
+    <t>c10092026</t>
+  </si>
+  <si>
+    <t>CMa12026</t>
   </si>
 </sst>
 </file>
@@ -397,13 +397,13 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
